--- a/exploratory_data_analysis/risultati/statistiche_descrittive.xlsx
+++ b/exploratory_data_analysis/risultati/statistiche_descrittive.xlsx
@@ -542,67 +542,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2816</v>
+        <v>2736</v>
       </c>
       <c r="C2" t="n">
-        <v>2816</v>
+        <v>2736</v>
       </c>
       <c r="D2" t="n">
-        <v>2816</v>
+        <v>2736</v>
       </c>
       <c r="E2" t="n">
-        <v>2816</v>
+        <v>2736</v>
       </c>
       <c r="F2" t="n">
-        <v>2816</v>
+        <v>2736</v>
       </c>
       <c r="G2" t="n">
-        <v>2816</v>
+        <v>2736</v>
       </c>
       <c r="H2" t="n">
-        <v>2816</v>
+        <v>2736</v>
       </c>
       <c r="I2" t="n">
-        <v>2816</v>
+        <v>2736</v>
       </c>
       <c r="J2" t="n">
-        <v>2816</v>
+        <v>2736</v>
       </c>
       <c r="K2" t="n">
-        <v>2816</v>
+        <v>2736</v>
       </c>
       <c r="L2" t="n">
-        <v>2816</v>
+        <v>2736</v>
       </c>
       <c r="M2" t="n">
-        <v>2816</v>
+        <v>2736</v>
       </c>
       <c r="N2" t="n">
-        <v>2816</v>
+        <v>2736</v>
       </c>
       <c r="O2" t="n">
-        <v>2816</v>
+        <v>2736</v>
       </c>
       <c r="P2" t="n">
-        <v>2816</v>
+        <v>2736</v>
       </c>
       <c r="Q2" t="n">
-        <v>2816</v>
+        <v>2736</v>
       </c>
       <c r="R2" t="n">
-        <v>2816</v>
+        <v>2736</v>
       </c>
       <c r="S2" t="n">
-        <v>2816</v>
+        <v>2736</v>
       </c>
       <c r="T2" t="n">
-        <v>2816</v>
+        <v>2736</v>
       </c>
       <c r="U2" t="n">
-        <v>2816</v>
+        <v>2736</v>
       </c>
       <c r="V2" t="n">
-        <v>2816</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="3">
@@ -612,67 +612,67 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>335.8500513668811</v>
+        <v>320.288530915809</v>
       </c>
       <c r="C3" t="n">
-        <v>19538.28835227273</v>
+        <v>19456.76498538012</v>
       </c>
       <c r="D3" t="n">
-        <v>184.2191869047439</v>
+        <v>178.0707293410548</v>
       </c>
       <c r="E3" t="n">
-        <v>3311.310780023798</v>
+        <v>3291.897765996209</v>
       </c>
       <c r="F3" t="n">
-        <v>183.8495441453534</v>
+        <v>181.8270959321153</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5159514802339178</v>
+        <v>0.5146606913250859</v>
       </c>
       <c r="H3" t="n">
-        <v>272.2813550143085</v>
+        <v>3.58541783710352</v>
       </c>
       <c r="I3" t="n">
-        <v>353022272.4378551</v>
+        <v>368361600.0452071</v>
       </c>
       <c r="J3" t="n">
-        <v>24936.7918294101</v>
+        <v>20074.87284515543</v>
       </c>
       <c r="K3" t="n">
-        <v>107.3018110795454</v>
+        <v>108.1126096491228</v>
       </c>
       <c r="L3" t="n">
-        <v>98566300.52308239</v>
+        <v>91837287.51608187</v>
       </c>
       <c r="M3" t="n">
-        <v>22.88996317588195</v>
+        <v>22.79750020687123</v>
       </c>
       <c r="N3" t="n">
-        <v>2.016149834758788</v>
+        <v>2.01559021703446</v>
       </c>
       <c r="O3" t="n">
-        <v>631.1230527348648</v>
+        <v>642.7023486229724</v>
       </c>
       <c r="P3" t="n">
-        <v>1575.582664968656</v>
+        <v>1558.494683173361</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.92215305778452</v>
+        <v>3.918410325869482</v>
       </c>
       <c r="R3" t="n">
-        <v>2.755620547231625</v>
+        <v>2.770811126158948</v>
       </c>
       <c r="S3" t="n">
-        <v>2.522677301478346</v>
+        <v>2.50574516678883</v>
       </c>
       <c r="T3" t="n">
-        <v>2.051705854725292</v>
+        <v>1.971219712469887</v>
       </c>
       <c r="U3" t="n">
-        <v>41.5954881230937</v>
+        <v>41.5145742480835</v>
       </c>
       <c r="V3" t="n">
-        <v>280.5369318181818</v>
+        <v>281.1962719298245</v>
       </c>
     </row>
     <row r="4">
@@ -682,67 +682,67 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2504.095167041302</v>
+        <v>2225.638396288761</v>
       </c>
       <c r="C4" t="n">
-        <v>77322.67332594823</v>
+        <v>77555.03441525697</v>
       </c>
       <c r="D4" t="n">
-        <v>377.8252740542516</v>
+        <v>375.9024184178274</v>
       </c>
       <c r="E4" t="n">
-        <v>1176.832281816331</v>
+        <v>1178.978898353756</v>
       </c>
       <c r="F4" t="n">
-        <v>173.9280837838404</v>
+        <v>172.0007794221645</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1869414526831369</v>
+        <v>0.1885384736748264</v>
       </c>
       <c r="H4" t="n">
-        <v>4880.815909770809</v>
+        <v>11.0093836351871</v>
       </c>
       <c r="I4" t="n">
-        <v>1987663824.966465</v>
+        <v>2039112454.075772</v>
       </c>
       <c r="J4" t="n">
-        <v>149795.6412292125</v>
+        <v>19535.53724536365</v>
       </c>
       <c r="K4" t="n">
-        <v>1992.986313204046</v>
+        <v>2019.256884673575</v>
       </c>
       <c r="L4" t="n">
-        <v>1832461471.527361</v>
+        <v>1790451760.097511</v>
       </c>
       <c r="M4" t="n">
-        <v>6.787362310290565</v>
+        <v>6.815510575137362</v>
       </c>
       <c r="N4" t="n">
-        <v>1.011489873368106</v>
+        <v>1.020628778407496</v>
       </c>
       <c r="O4" t="n">
-        <v>1220.306885261246</v>
+        <v>1227.943879648653</v>
       </c>
       <c r="P4" t="n">
-        <v>949.6776775657595</v>
+        <v>952.1208913182115</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5809819983606899</v>
+        <v>0.5827628089251643</v>
       </c>
       <c r="R4" t="n">
-        <v>6.146283319327261</v>
+        <v>6.210745833011489</v>
       </c>
       <c r="S4" t="n">
-        <v>12.55338215028832</v>
+        <v>12.52800374775808</v>
       </c>
       <c r="T4" t="n">
-        <v>8.340088375615998</v>
+        <v>8.255237950692084</v>
       </c>
       <c r="U4" t="n">
-        <v>30.55507055760171</v>
+        <v>30.60383302137502</v>
       </c>
       <c r="V4" t="n">
-        <v>393.0541505225678</v>
+        <v>396.1055689993668</v>
       </c>
     </row>
     <row r="5">
@@ -773,10 +773,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>204828</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>577</v>
       </c>
       <c r="K5" t="n">
         <v>-7.105427357601002e-14</v>
@@ -822,31 +822,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.992980599935001</v>
+        <v>10.007699383425</v>
       </c>
       <c r="C6" t="n">
-        <v>610.75</v>
+        <v>593</v>
       </c>
       <c r="D6" t="n">
-        <v>24.75695113704502</v>
+        <v>24.38240113820417</v>
       </c>
       <c r="E6" t="n">
-        <v>2450.148428958882</v>
+        <v>2429.12666317147</v>
       </c>
       <c r="F6" t="n">
-        <v>47.40897347130547</v>
+        <v>46.12133486670739</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3763790077868392</v>
+        <v>0.3733514162194859</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>4707797.5</v>
+        <v>6045462.97307465</v>
       </c>
       <c r="J6" t="n">
-        <v>3412.387756347656</v>
+        <v>4465</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -855,22 +855,22 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>18.74574959299784</v>
+        <v>18.63869539896649</v>
       </c>
       <c r="N6" t="n">
-        <v>1.272004125389327</v>
+        <v>1.258729136583092</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>499.7310536861426</v>
+        <v>479.6622016143796</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.647791922092438</v>
+        <v>3.637920200824738</v>
       </c>
       <c r="R6" t="n">
-        <v>1.304136902093887</v>
+        <v>1.304867506027222</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -879,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>15.64823401678548</v>
+        <v>15.56122696349549</v>
       </c>
       <c r="V6" t="n">
         <v>44</v>
@@ -892,31 +892,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.41742771085</v>
+        <v>26.36959805225</v>
       </c>
       <c r="C7" t="n">
-        <v>1681</v>
+        <v>1623.5</v>
       </c>
       <c r="D7" t="n">
-        <v>68.71819763339096</v>
+        <v>66.17086868870709</v>
       </c>
       <c r="E7" t="n">
-        <v>3263.414462278078</v>
+        <v>3241.854034301131</v>
       </c>
       <c r="F7" t="n">
-        <v>128.7331585301973</v>
+        <v>126.3501521243566</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5042992577559561</v>
+        <v>0.5016595630514513</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>19252674</v>
+        <v>21780823.39224711</v>
       </c>
       <c r="J7" t="n">
-        <v>9620.75927734375</v>
+        <v>12025</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -925,22 +925,22 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>26.65551429823392</v>
+        <v>26.62771288553876</v>
       </c>
       <c r="N7" t="n">
-        <v>2.004857327127639</v>
+        <v>1.995144242343182</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2062.071040153503</v>
+        <v>2039.950061504657</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.996812701225281</v>
+        <v>3.986884474754333</v>
       </c>
       <c r="R7" t="n">
-        <v>1.461325585842133</v>
+        <v>1.462561845779419</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -949,10 +949,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>34.37975783882192</v>
+        <v>34.20183389023812</v>
       </c>
       <c r="V7" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8">
@@ -962,55 +962,55 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>96.528163604</v>
+        <v>98.32418531425</v>
       </c>
       <c r="C8" t="n">
-        <v>6743.5</v>
+        <v>6259</v>
       </c>
       <c r="D8" t="n">
-        <v>185.3942503679985</v>
+        <v>173.8929336902572</v>
       </c>
       <c r="E8" t="n">
-        <v>4204.793739211927</v>
+        <v>4173.546025584545</v>
       </c>
       <c r="F8" t="n">
-        <v>279.1974046901863</v>
+        <v>277.4768353649193</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6364849495433643</v>
+        <v>0.6360433029020202</v>
       </c>
       <c r="H8" t="n">
-        <v>4.988465931733683</v>
+        <v>3.152169036120929</v>
       </c>
       <c r="I8" t="n">
-        <v>90580018</v>
+        <v>93633771.65717489</v>
       </c>
       <c r="J8" t="n">
-        <v>25868.75146484375</v>
+        <v>33345.25</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>73144.75</v>
+        <v>78839</v>
       </c>
       <c r="M8" t="n">
-        <v>27.4634787241618</v>
+        <v>27.45785426272431</v>
       </c>
       <c r="N8" t="n">
-        <v>2.628727065154817</v>
+        <v>2.632280723424628</v>
       </c>
       <c r="O8" t="n">
-        <v>607.9845529283799</v>
+        <v>649.2355682093914</v>
       </c>
       <c r="P8" t="n">
-        <v>2361.729965209961</v>
+        <v>2359.349702272545</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.288117408752441</v>
+        <v>4.289039850234985</v>
       </c>
       <c r="R8" t="n">
-        <v>1.915650635957718</v>
+        <v>1.93812695145607</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1019,7 +1019,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>66.23636341718606</v>
+        <v>66.15938527126622</v>
       </c>
       <c r="V8" t="n">
         <v>351.25</v>
@@ -1050,13 +1050,13 @@
         <v>1.63834005044413</v>
       </c>
       <c r="H9" t="n">
-        <v>245118.8993713753</v>
+        <v>232.3907979412545</v>
       </c>
       <c r="I9" t="n">
-        <v>44217348096</v>
+        <v>39929647374.92642</v>
       </c>
       <c r="J9" t="n">
-        <v>7311805.5</v>
+        <v>144634.4446974098</v>
       </c>
       <c r="K9" t="n">
         <v>103215.4</v>
